--- a/feature_summary_by_label.xlsx
+++ b/feature_summary_by_label.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="label_0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="label_1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="label_2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,28 +491,28 @@
         <v>1000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07568359020852218</v>
+        <v>0.1140534550195567</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02459977757530131</v>
+        <v>0.0353762120802573</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0018132366273798</v>
+        <v>0.007822685788787399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0625566636446056</v>
+        <v>0.0951760104302477</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0788757932910244</v>
+        <v>0.1186440677966101</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08975521305530371</v>
+        <v>0.1342894393741851</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1758839528558476</v>
+        <v>0.258148631029987</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006051490567542973</v>
+        <v>0.001251476381147342</v>
       </c>
     </row>
     <row r="3">
@@ -525,28 +525,28 @@
         <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1857028133332066</v>
+        <v>0.1465472539992571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03945825879831765</v>
+        <v>0.03779895528436047</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0327224086901708</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1766470783495399</v>
+        <v>0.1378723318881672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1817874498204099</v>
+        <v>0.1427965398306803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1884060377677774</v>
+        <v>0.1491368021100392</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4676222013073904</v>
+        <v>0.4166113334685922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001556954187395012</v>
+        <v>0.001428761020589082</v>
       </c>
     </row>
     <row r="4">
@@ -559,28 +559,28 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07879440937781783</v>
+        <v>0.1216275773195876</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02338737251101736</v>
+        <v>0.03342344860144105</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0072137060414788</v>
+        <v>0.0193298969072164</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06762849413886381</v>
+        <v>0.1056701030927835</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08205590622182141</v>
+        <v>0.1262886597938144</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0946798917944093</v>
+        <v>0.1443298969072164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1505861136158701</v>
+        <v>0.2242268041237113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0005469691929690906</v>
+        <v>0.001117126916413172</v>
       </c>
     </row>
     <row r="5">
@@ -593,28 +593,28 @@
         <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5208929004722479</v>
+        <v>0.5431480078454985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1574565379043534</v>
+        <v>0.1501424902495894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09166898641240449</v>
+        <v>0.1338620665353481</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3973889780061042</v>
+        <v>0.4253809927602116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5224304576021583</v>
+        <v>0.5446141435770361</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6275782294866497</v>
+        <v>0.6448776735964954</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02479256132882507</v>
+        <v>0.02254276737834807</v>
       </c>
     </row>
     <row r="6">
@@ -661,28 +661,28 @@
         <v>1000</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2655782599431614</v>
+        <v>0.2277124736707379</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1464549531965155</v>
+        <v>0.1223725374772518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0464407259600008</v>
+        <v>0.0446089629684117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1874201758106442</v>
+        <v>0.1624063650625641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2235290954926694</v>
+        <v>0.1925776909932247</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3323220472915328</v>
+        <v>0.2834812028287262</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8772338401958414</v>
+        <v>0.7387900697777583</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02144905331579354</v>
+        <v>0.0149750379286214</v>
       </c>
     </row>
   </sheetData>
@@ -761,28 +761,28 @@
         <v>1000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1052846781504986</v>
+        <v>0.1043885267275097</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1028525469508842</v>
+        <v>0.06121006238747823</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0652765185856754</v>
+        <v>0.0638852672750977</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0698096101541251</v>
+        <v>0.0964797913950456</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08544877606527648</v>
+        <v>0.1316818774445893</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01057864641428383</v>
+        <v>0.003746671737478977</v>
       </c>
     </row>
     <row r="3">
@@ -795,28 +795,28 @@
         <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2106763353540037</v>
+        <v>0.1770027190566642</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1316954489543057</v>
+        <v>0.08480743997795731</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0010087667648949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1680277538245668</v>
+        <v>0.1345146648297046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1817874498204099</v>
+        <v>0.1565354310551531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1949429540369483</v>
+        <v>0.2341185631877616</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01734369127527615</v>
+        <v>0.007192301875614832</v>
       </c>
     </row>
     <row r="4">
@@ -829,28 +829,28 @@
         <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1153922452660054</v>
+        <v>0.1484574742268041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1057167185215431</v>
+        <v>0.0604563136764211</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0721370604147881</v>
+        <v>0.1159793814432989</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0757439134355275</v>
+        <v>0.1378865979381443</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1118124436429215</v>
+        <v>0.1829896907216494</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01117602457496317</v>
+        <v>0.00365496586334182</v>
       </c>
     </row>
     <row r="5">
@@ -863,28 +863,28 @@
         <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2187685800192563</v>
+        <v>0.4217250292763053</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1066109019513398</v>
+        <v>0.2071961027045016</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1555185976686203</v>
+        <v>0.2739134729427</v>
       </c>
       <c r="G5" t="n">
-        <v>0.200944018292197</v>
+        <v>0.357926129611507</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2483723971232999</v>
+        <v>0.5192176447644272</v>
       </c>
       <c r="I5" t="n">
-        <v>0.801199999696209</v>
+        <v>0.990553625325458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0113658844148782</v>
+        <v>0.04293022497593438</v>
       </c>
     </row>
     <row r="6">
@@ -897,28 +897,28 @@
         <v>1000</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2980789373069133</v>
+        <v>0.5047610566305831</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04286203170870115</v>
+        <v>0.1441990858307524</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04223315238709</v>
+        <v>0.0763729265983514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2756431088968446</v>
+        <v>0.4282117129371594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2923020618984461</v>
+        <v>0.5136710376119349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3184131967570875</v>
+        <v>0.57680019893419</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7080516827052749</v>
+        <v>0.974962789830324</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001837153762197703</v>
+        <v>0.0207933763544247</v>
       </c>
     </row>
     <row r="7">
@@ -931,28 +931,28 @@
         <v>1000</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1018519098653283</v>
+        <v>0.436220060377562</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0780401547224025</v>
+        <v>0.1790928346332725</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06514903944103011</v>
+        <v>0.3216040727005818</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0897407659469355</v>
+        <v>0.4169620971928946</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1085165517766672</v>
+        <v>0.5257370367717884</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00609026574909652</v>
+        <v>0.0320742434169807</v>
       </c>
     </row>
   </sheetData>
